--- a/inst/Instructions.xlsx
+++ b/inst/Instructions.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/martics/Documents/GitHub/PhenotypeR/inst/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1B7247F-C55B-3348-B165-143A02EDE95E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A15D251C-2F7C-BF4D-A38A-CE408E5C273D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17420" xr2:uid="{CDA5D9F4-215A-E946-86DB-1C84C02DBC91}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17420" activeTab="1" xr2:uid="{CDA5D9F4-215A-E946-86DB-1C84C02DBC91}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
+    <sheet name="Specifications" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
   <si>
     <t>Overview</t>
   </si>
@@ -254,6 +255,343 @@
     </r>
   </si>
   <si>
+    <t>Cohort name</t>
+  </si>
+  <si>
+    <t>Database diagnostics</t>
+  </si>
+  <si>
+    <t>Codelist diagnostics</t>
+  </si>
+  <si>
+    <t>Cohort diagnostics</t>
+  </si>
+  <si>
+    <t>Population Diagnostics</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Person Table Summary
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="2" tint="-0.499984740745262"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t>(TRUE/FALSE)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Observation Table Summary
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="2" tint="-0.499984740745262"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t>(TRUE/FALSE)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Clinical Records Summary
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="2" tint="-0.499984740745262"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t>(TRUE/FALSE)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Achilles code use
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="2" tint="-0.499984740745262"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t>(TRUE/FALSE)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Orphan code use
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="2" tint="-0.499984740745262"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t>(TRUE/FALSE)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Cohort code use
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="2" tint="-0.499984740745262"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t>(TRUE/FALSE)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Drug diagnostics
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="2" tint="-0.499984740745262"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t>(TRUE/FALSE)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Drug diagnostics sample
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="2" tint="-0.499984740745262"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t>(numeric value)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Measurement Diagnostics
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="2" tint="-0.499984740745262"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t>(TRUE/FALSE)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Measurement Diagnostics Sample
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="2" tint="-0.499984740745262"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t>(numeric value)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Cohort count
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="2" tint="-0.499984740745262"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t>(TRUE/FALSE)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Cohort characteristics
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="2" tint="-0.499984740745262"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t>(TRUE/FALSE)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">LSC
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="2" tint="-0.499984740745262"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t>(TRUE/FALSE)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Compare cohorts
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="2" tint="-0.499984740745262"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t>(TRUE/FALSE)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Cohort Survival
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="2" tint="-0.499984740745262"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t>(TRUE/FALSE)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Cohort overlap
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="2" tint="-0.499984740745262"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t>(TRUE/FALSE)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Cohort Sample
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="2" tint="-0.499984740745262"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t>(numeric value)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Matched Sample
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="2" tint="-0.499984740745262"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t>(numeric value)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Incidence
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="2" tint="-0.499984740745262"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t>(TRUE/FALSE)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Period Prevalence
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="2" tint="-0.499984740745262"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t>(TRUE/FALSE)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Population Sample
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="2" tint="-0.499984740745262"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t>(numeric value)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Date Range
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="2" tint="-0.499984740745262"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t>(Study period start/ Study period end)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Snapshot
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="2" tint="-0.499984740745262"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t>(TRUE/FALSE)</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -269,15 +607,18 @@
         <color rgb="FF000000"/>
         <rFont val="Aptos Narrow"/>
       </rPr>
-      <t xml:space="preserve"> Fill in the columns</t>
-    </r>
+      <t xml:space="preserve"> Fill in the columns. Missing (unpopulated) values will be interpreted as using the defaults as populated by the different functions in PhenotypeR.</t>
+    </r>
+  </si>
+  <si>
+    <t>abc</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -342,16 +683,48 @@
       <name val="Consolas"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="22"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="2" tint="-0.499984740745262"/>
+      <name val="Aptos Narrow (Body)"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -359,11 +732,330 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -382,6 +1074,66 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -773,9 +1525,9 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:1" ht="34" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16" spans="1:1" ht="25" x14ac:dyDescent="0.3">
@@ -796,4 +1548,1435 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66189217-AFFF-FF4C-96F8-B7D661B6748A}">
+  <dimension ref="A1:X52"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="27.83203125" customWidth="1"/>
+    <col min="2" max="24" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:24" ht="25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="30"/>
+      <c r="L1" s="31"/>
+      <c r="M1" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="N1" s="33"/>
+      <c r="O1" s="33"/>
+      <c r="P1" s="33"/>
+      <c r="Q1" s="33"/>
+      <c r="R1" s="33"/>
+      <c r="S1" s="33"/>
+      <c r="T1" s="34"/>
+      <c r="U1" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="V1" s="30"/>
+      <c r="W1" s="30"/>
+      <c r="X1" s="31"/>
+    </row>
+    <row r="2" spans="1:24" ht="101" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="28"/>
+      <c r="B2" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="K2" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L2" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="M2" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="N2" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O2" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="P2" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q2" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="R2" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="S2" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="T2" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="U2" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="V2" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="W2" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="X2" s="10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A3" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="20"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="21"/>
+      <c r="H3" s="21"/>
+      <c r="I3" s="21"/>
+      <c r="J3" s="21"/>
+      <c r="K3" s="21"/>
+      <c r="L3" s="22"/>
+      <c r="M3" s="20"/>
+      <c r="N3" s="21"/>
+      <c r="O3" s="21"/>
+      <c r="P3" s="21"/>
+      <c r="Q3" s="21"/>
+      <c r="R3" s="21"/>
+      <c r="S3" s="21"/>
+      <c r="T3" s="22"/>
+      <c r="U3" s="20"/>
+      <c r="V3" s="21"/>
+      <c r="W3" s="21"/>
+      <c r="X3" s="22"/>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A4" s="15"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="17"/>
+      <c r="L4" s="18"/>
+      <c r="M4" s="16"/>
+      <c r="N4" s="17"/>
+      <c r="O4" s="17"/>
+      <c r="P4" s="17"/>
+      <c r="Q4" s="17"/>
+      <c r="R4" s="17"/>
+      <c r="S4" s="17"/>
+      <c r="T4" s="18"/>
+      <c r="U4" s="16"/>
+      <c r="V4" s="17"/>
+      <c r="W4" s="17"/>
+      <c r="X4" s="18"/>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A5" s="15"/>
+      <c r="B5" s="16"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="17"/>
+      <c r="I5" s="17"/>
+      <c r="J5" s="17"/>
+      <c r="K5" s="17"/>
+      <c r="L5" s="18"/>
+      <c r="M5" s="16"/>
+      <c r="N5" s="17"/>
+      <c r="O5" s="17"/>
+      <c r="P5" s="17"/>
+      <c r="Q5" s="17"/>
+      <c r="R5" s="17"/>
+      <c r="S5" s="17"/>
+      <c r="T5" s="18"/>
+      <c r="U5" s="16"/>
+      <c r="V5" s="17"/>
+      <c r="W5" s="17"/>
+      <c r="X5" s="18"/>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A6" s="15"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17"/>
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="17"/>
+      <c r="L6" s="18"/>
+      <c r="M6" s="16"/>
+      <c r="N6" s="17"/>
+      <c r="O6" s="17"/>
+      <c r="P6" s="17"/>
+      <c r="Q6" s="17"/>
+      <c r="R6" s="17"/>
+      <c r="S6" s="17"/>
+      <c r="T6" s="18"/>
+      <c r="U6" s="16"/>
+      <c r="V6" s="17"/>
+      <c r="W6" s="17"/>
+      <c r="X6" s="18"/>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A7" s="15"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="17"/>
+      <c r="I7" s="17"/>
+      <c r="J7" s="17"/>
+      <c r="K7" s="17"/>
+      <c r="L7" s="18"/>
+      <c r="M7" s="16"/>
+      <c r="N7" s="17"/>
+      <c r="O7" s="17"/>
+      <c r="P7" s="17"/>
+      <c r="Q7" s="17"/>
+      <c r="R7" s="17"/>
+      <c r="S7" s="17"/>
+      <c r="T7" s="18"/>
+      <c r="U7" s="16"/>
+      <c r="V7" s="17"/>
+      <c r="W7" s="17"/>
+      <c r="X7" s="18"/>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A8" s="15"/>
+      <c r="B8" s="16"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="17"/>
+      <c r="I8" s="17"/>
+      <c r="J8" s="17"/>
+      <c r="K8" s="17"/>
+      <c r="L8" s="18"/>
+      <c r="M8" s="16"/>
+      <c r="N8" s="17"/>
+      <c r="O8" s="17"/>
+      <c r="P8" s="17"/>
+      <c r="Q8" s="17"/>
+      <c r="R8" s="17"/>
+      <c r="S8" s="17"/>
+      <c r="T8" s="18"/>
+      <c r="U8" s="16"/>
+      <c r="V8" s="17"/>
+      <c r="W8" s="17"/>
+      <c r="X8" s="18"/>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A9" s="15"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="17"/>
+      <c r="I9" s="17"/>
+      <c r="J9" s="17"/>
+      <c r="K9" s="17"/>
+      <c r="L9" s="18"/>
+      <c r="M9" s="16"/>
+      <c r="N9" s="17"/>
+      <c r="O9" s="17"/>
+      <c r="P9" s="17"/>
+      <c r="Q9" s="17"/>
+      <c r="R9" s="17"/>
+      <c r="S9" s="17"/>
+      <c r="T9" s="18"/>
+      <c r="U9" s="16"/>
+      <c r="V9" s="17"/>
+      <c r="W9" s="17"/>
+      <c r="X9" s="18"/>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A10" s="15"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="17"/>
+      <c r="I10" s="17"/>
+      <c r="J10" s="17"/>
+      <c r="K10" s="17"/>
+      <c r="L10" s="18"/>
+      <c r="M10" s="16"/>
+      <c r="N10" s="17"/>
+      <c r="O10" s="17"/>
+      <c r="P10" s="17"/>
+      <c r="Q10" s="17"/>
+      <c r="R10" s="17"/>
+      <c r="S10" s="17"/>
+      <c r="T10" s="18"/>
+      <c r="U10" s="16"/>
+      <c r="V10" s="17"/>
+      <c r="W10" s="17"/>
+      <c r="X10" s="18"/>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A11" s="15"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="17"/>
+      <c r="I11" s="17"/>
+      <c r="J11" s="17"/>
+      <c r="K11" s="17"/>
+      <c r="L11" s="18"/>
+      <c r="M11" s="16"/>
+      <c r="N11" s="17"/>
+      <c r="O11" s="17"/>
+      <c r="P11" s="17"/>
+      <c r="Q11" s="17"/>
+      <c r="R11" s="17"/>
+      <c r="S11" s="17"/>
+      <c r="T11" s="18"/>
+      <c r="U11" s="16"/>
+      <c r="V11" s="17"/>
+      <c r="W11" s="17"/>
+      <c r="X11" s="18"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A12" s="15"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="17"/>
+      <c r="I12" s="17"/>
+      <c r="J12" s="17"/>
+      <c r="K12" s="17"/>
+      <c r="L12" s="18"/>
+      <c r="M12" s="16"/>
+      <c r="N12" s="17"/>
+      <c r="O12" s="17"/>
+      <c r="P12" s="17"/>
+      <c r="Q12" s="17"/>
+      <c r="R12" s="17"/>
+      <c r="S12" s="17"/>
+      <c r="T12" s="18"/>
+      <c r="U12" s="16"/>
+      <c r="V12" s="17"/>
+      <c r="W12" s="17"/>
+      <c r="X12" s="18"/>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A13" s="15"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="17"/>
+      <c r="I13" s="17"/>
+      <c r="J13" s="17"/>
+      <c r="K13" s="17"/>
+      <c r="L13" s="18"/>
+      <c r="M13" s="16"/>
+      <c r="N13" s="17"/>
+      <c r="O13" s="17"/>
+      <c r="P13" s="17"/>
+      <c r="Q13" s="17"/>
+      <c r="R13" s="17"/>
+      <c r="S13" s="17"/>
+      <c r="T13" s="18"/>
+      <c r="U13" s="16"/>
+      <c r="V13" s="17"/>
+      <c r="W13" s="17"/>
+      <c r="X13" s="18"/>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A14" s="15"/>
+      <c r="B14" s="16"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="17"/>
+      <c r="I14" s="17"/>
+      <c r="J14" s="17"/>
+      <c r="K14" s="17"/>
+      <c r="L14" s="18"/>
+      <c r="M14" s="16"/>
+      <c r="N14" s="17"/>
+      <c r="O14" s="17"/>
+      <c r="P14" s="17"/>
+      <c r="Q14" s="17"/>
+      <c r="R14" s="17"/>
+      <c r="S14" s="17"/>
+      <c r="T14" s="18"/>
+      <c r="U14" s="16"/>
+      <c r="V14" s="17"/>
+      <c r="W14" s="17"/>
+      <c r="X14" s="18"/>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A15" s="15"/>
+      <c r="B15" s="16"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="17"/>
+      <c r="I15" s="17"/>
+      <c r="J15" s="17"/>
+      <c r="K15" s="17"/>
+      <c r="L15" s="18"/>
+      <c r="M15" s="16"/>
+      <c r="N15" s="17"/>
+      <c r="O15" s="17"/>
+      <c r="P15" s="17"/>
+      <c r="Q15" s="17"/>
+      <c r="R15" s="17"/>
+      <c r="S15" s="17"/>
+      <c r="T15" s="18"/>
+      <c r="U15" s="16"/>
+      <c r="V15" s="17"/>
+      <c r="W15" s="17"/>
+      <c r="X15" s="18"/>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A16" s="15"/>
+      <c r="B16" s="16"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="17"/>
+      <c r="H16" s="17"/>
+      <c r="I16" s="17"/>
+      <c r="J16" s="17"/>
+      <c r="K16" s="17"/>
+      <c r="L16" s="18"/>
+      <c r="M16" s="16"/>
+      <c r="N16" s="17"/>
+      <c r="O16" s="17"/>
+      <c r="P16" s="17"/>
+      <c r="Q16" s="17"/>
+      <c r="R16" s="17"/>
+      <c r="S16" s="17"/>
+      <c r="T16" s="18"/>
+      <c r="U16" s="16"/>
+      <c r="V16" s="17"/>
+      <c r="W16" s="17"/>
+      <c r="X16" s="18"/>
+    </row>
+    <row r="17" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A17" s="15"/>
+      <c r="B17" s="16"/>
+      <c r="C17" s="17"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="17"/>
+      <c r="I17" s="17"/>
+      <c r="J17" s="17"/>
+      <c r="K17" s="17"/>
+      <c r="L17" s="18"/>
+      <c r="M17" s="16"/>
+      <c r="N17" s="17"/>
+      <c r="O17" s="17"/>
+      <c r="P17" s="17"/>
+      <c r="Q17" s="17"/>
+      <c r="R17" s="17"/>
+      <c r="S17" s="17"/>
+      <c r="T17" s="18"/>
+      <c r="U17" s="16"/>
+      <c r="V17" s="17"/>
+      <c r="W17" s="17"/>
+      <c r="X17" s="18"/>
+    </row>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A18" s="15"/>
+      <c r="B18" s="16"/>
+      <c r="C18" s="17"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="17"/>
+      <c r="I18" s="17"/>
+      <c r="J18" s="17"/>
+      <c r="K18" s="17"/>
+      <c r="L18" s="18"/>
+      <c r="M18" s="16"/>
+      <c r="N18" s="17"/>
+      <c r="O18" s="17"/>
+      <c r="P18" s="17"/>
+      <c r="Q18" s="17"/>
+      <c r="R18" s="17"/>
+      <c r="S18" s="17"/>
+      <c r="T18" s="18"/>
+      <c r="U18" s="16"/>
+      <c r="V18" s="17"/>
+      <c r="W18" s="17"/>
+      <c r="X18" s="18"/>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A19" s="15"/>
+      <c r="B19" s="16"/>
+      <c r="C19" s="17"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="16"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="17"/>
+      <c r="I19" s="17"/>
+      <c r="J19" s="17"/>
+      <c r="K19" s="17"/>
+      <c r="L19" s="18"/>
+      <c r="M19" s="16"/>
+      <c r="N19" s="17"/>
+      <c r="O19" s="17"/>
+      <c r="P19" s="17"/>
+      <c r="Q19" s="17"/>
+      <c r="R19" s="17"/>
+      <c r="S19" s="17"/>
+      <c r="T19" s="18"/>
+      <c r="U19" s="16"/>
+      <c r="V19" s="17"/>
+      <c r="W19" s="17"/>
+      <c r="X19" s="18"/>
+    </row>
+    <row r="20" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A20" s="15"/>
+      <c r="B20" s="16"/>
+      <c r="C20" s="17"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="16"/>
+      <c r="G20" s="17"/>
+      <c r="H20" s="17"/>
+      <c r="I20" s="17"/>
+      <c r="J20" s="17"/>
+      <c r="K20" s="17"/>
+      <c r="L20" s="18"/>
+      <c r="M20" s="16"/>
+      <c r="N20" s="17"/>
+      <c r="O20" s="17"/>
+      <c r="P20" s="17"/>
+      <c r="Q20" s="17"/>
+      <c r="R20" s="17"/>
+      <c r="S20" s="17"/>
+      <c r="T20" s="18"/>
+      <c r="U20" s="16"/>
+      <c r="V20" s="17"/>
+      <c r="W20" s="17"/>
+      <c r="X20" s="18"/>
+    </row>
+    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A21" s="15"/>
+      <c r="B21" s="16"/>
+      <c r="C21" s="17"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="16"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="17"/>
+      <c r="I21" s="17"/>
+      <c r="J21" s="17"/>
+      <c r="K21" s="17"/>
+      <c r="L21" s="18"/>
+      <c r="M21" s="16"/>
+      <c r="N21" s="17"/>
+      <c r="O21" s="17"/>
+      <c r="P21" s="17"/>
+      <c r="Q21" s="17"/>
+      <c r="R21" s="17"/>
+      <c r="S21" s="17"/>
+      <c r="T21" s="18"/>
+      <c r="U21" s="16"/>
+      <c r="V21" s="17"/>
+      <c r="W21" s="17"/>
+      <c r="X21" s="18"/>
+    </row>
+    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A22" s="15"/>
+      <c r="B22" s="16"/>
+      <c r="C22" s="17"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="17"/>
+      <c r="H22" s="17"/>
+      <c r="I22" s="17"/>
+      <c r="J22" s="17"/>
+      <c r="K22" s="17"/>
+      <c r="L22" s="18"/>
+      <c r="M22" s="16"/>
+      <c r="N22" s="17"/>
+      <c r="O22" s="17"/>
+      <c r="P22" s="17"/>
+      <c r="Q22" s="17"/>
+      <c r="R22" s="17"/>
+      <c r="S22" s="17"/>
+      <c r="T22" s="18"/>
+      <c r="U22" s="16"/>
+      <c r="V22" s="17"/>
+      <c r="W22" s="17"/>
+      <c r="X22" s="18"/>
+    </row>
+    <row r="23" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A23" s="15"/>
+      <c r="B23" s="16"/>
+      <c r="C23" s="17"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="16"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="17"/>
+      <c r="I23" s="17"/>
+      <c r="J23" s="17"/>
+      <c r="K23" s="17"/>
+      <c r="L23" s="18"/>
+      <c r="M23" s="16"/>
+      <c r="N23" s="17"/>
+      <c r="O23" s="17"/>
+      <c r="P23" s="17"/>
+      <c r="Q23" s="17"/>
+      <c r="R23" s="17"/>
+      <c r="S23" s="17"/>
+      <c r="T23" s="18"/>
+      <c r="U23" s="16"/>
+      <c r="V23" s="17"/>
+      <c r="W23" s="17"/>
+      <c r="X23" s="18"/>
+    </row>
+    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A24" s="15"/>
+      <c r="B24" s="16"/>
+      <c r="C24" s="17"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="16"/>
+      <c r="G24" s="17"/>
+      <c r="H24" s="17"/>
+      <c r="I24" s="17"/>
+      <c r="J24" s="17"/>
+      <c r="K24" s="17"/>
+      <c r="L24" s="18"/>
+      <c r="M24" s="16"/>
+      <c r="N24" s="17"/>
+      <c r="O24" s="17"/>
+      <c r="P24" s="17"/>
+      <c r="Q24" s="17"/>
+      <c r="R24" s="17"/>
+      <c r="S24" s="17"/>
+      <c r="T24" s="18"/>
+      <c r="U24" s="16"/>
+      <c r="V24" s="17"/>
+      <c r="W24" s="17"/>
+      <c r="X24" s="18"/>
+    </row>
+    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A25" s="15"/>
+      <c r="B25" s="16"/>
+      <c r="C25" s="17"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="16"/>
+      <c r="G25" s="17"/>
+      <c r="H25" s="17"/>
+      <c r="I25" s="17"/>
+      <c r="J25" s="17"/>
+      <c r="K25" s="17"/>
+      <c r="L25" s="18"/>
+      <c r="M25" s="16"/>
+      <c r="N25" s="17"/>
+      <c r="O25" s="17"/>
+      <c r="P25" s="17"/>
+      <c r="Q25" s="17"/>
+      <c r="R25" s="17"/>
+      <c r="S25" s="17"/>
+      <c r="T25" s="18"/>
+      <c r="U25" s="16"/>
+      <c r="V25" s="17"/>
+      <c r="W25" s="17"/>
+      <c r="X25" s="18"/>
+    </row>
+    <row r="26" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A26" s="15"/>
+      <c r="B26" s="16"/>
+      <c r="C26" s="17"/>
+      <c r="D26" s="17"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="16"/>
+      <c r="G26" s="17"/>
+      <c r="H26" s="17"/>
+      <c r="I26" s="17"/>
+      <c r="J26" s="17"/>
+      <c r="K26" s="17"/>
+      <c r="L26" s="18"/>
+      <c r="M26" s="16"/>
+      <c r="N26" s="17"/>
+      <c r="O26" s="17"/>
+      <c r="P26" s="17"/>
+      <c r="Q26" s="17"/>
+      <c r="R26" s="17"/>
+      <c r="S26" s="17"/>
+      <c r="T26" s="18"/>
+      <c r="U26" s="16"/>
+      <c r="V26" s="17"/>
+      <c r="W26" s="17"/>
+      <c r="X26" s="18"/>
+    </row>
+    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A27" s="15"/>
+      <c r="B27" s="16"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="16"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="17"/>
+      <c r="I27" s="17"/>
+      <c r="J27" s="17"/>
+      <c r="K27" s="17"/>
+      <c r="L27" s="18"/>
+      <c r="M27" s="16"/>
+      <c r="N27" s="17"/>
+      <c r="O27" s="17"/>
+      <c r="P27" s="17"/>
+      <c r="Q27" s="17"/>
+      <c r="R27" s="17"/>
+      <c r="S27" s="17"/>
+      <c r="T27" s="18"/>
+      <c r="U27" s="16"/>
+      <c r="V27" s="17"/>
+      <c r="W27" s="17"/>
+      <c r="X27" s="18"/>
+    </row>
+    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A28" s="15"/>
+      <c r="B28" s="16"/>
+      <c r="C28" s="17"/>
+      <c r="D28" s="17"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="16"/>
+      <c r="G28" s="17"/>
+      <c r="H28" s="17"/>
+      <c r="I28" s="17"/>
+      <c r="J28" s="17"/>
+      <c r="K28" s="17"/>
+      <c r="L28" s="18"/>
+      <c r="M28" s="16"/>
+      <c r="N28" s="17"/>
+      <c r="O28" s="17"/>
+      <c r="P28" s="17"/>
+      <c r="Q28" s="17"/>
+      <c r="R28" s="17"/>
+      <c r="S28" s="17"/>
+      <c r="T28" s="18"/>
+      <c r="U28" s="16"/>
+      <c r="V28" s="17"/>
+      <c r="W28" s="17"/>
+      <c r="X28" s="18"/>
+    </row>
+    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A29" s="15"/>
+      <c r="B29" s="16"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="17"/>
+      <c r="E29" s="18"/>
+      <c r="F29" s="16"/>
+      <c r="G29" s="17"/>
+      <c r="H29" s="17"/>
+      <c r="I29" s="17"/>
+      <c r="J29" s="17"/>
+      <c r="K29" s="17"/>
+      <c r="L29" s="18"/>
+      <c r="M29" s="16"/>
+      <c r="N29" s="17"/>
+      <c r="O29" s="17"/>
+      <c r="P29" s="17"/>
+      <c r="Q29" s="17"/>
+      <c r="R29" s="17"/>
+      <c r="S29" s="17"/>
+      <c r="T29" s="18"/>
+      <c r="U29" s="16"/>
+      <c r="V29" s="17"/>
+      <c r="W29" s="17"/>
+      <c r="X29" s="18"/>
+    </row>
+    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A30" s="15"/>
+      <c r="B30" s="16"/>
+      <c r="C30" s="17"/>
+      <c r="D30" s="17"/>
+      <c r="E30" s="18"/>
+      <c r="F30" s="16"/>
+      <c r="G30" s="17"/>
+      <c r="H30" s="17"/>
+      <c r="I30" s="17"/>
+      <c r="J30" s="17"/>
+      <c r="K30" s="17"/>
+      <c r="L30" s="18"/>
+      <c r="M30" s="16"/>
+      <c r="N30" s="17"/>
+      <c r="O30" s="17"/>
+      <c r="P30" s="17"/>
+      <c r="Q30" s="17"/>
+      <c r="R30" s="17"/>
+      <c r="S30" s="17"/>
+      <c r="T30" s="18"/>
+      <c r="U30" s="16"/>
+      <c r="V30" s="17"/>
+      <c r="W30" s="17"/>
+      <c r="X30" s="18"/>
+    </row>
+    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A31" s="15"/>
+      <c r="B31" s="16"/>
+      <c r="C31" s="17"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="18"/>
+      <c r="F31" s="16"/>
+      <c r="G31" s="17"/>
+      <c r="H31" s="17"/>
+      <c r="I31" s="17"/>
+      <c r="J31" s="17"/>
+      <c r="K31" s="17"/>
+      <c r="L31" s="18"/>
+      <c r="M31" s="16"/>
+      <c r="N31" s="17"/>
+      <c r="O31" s="17"/>
+      <c r="P31" s="17"/>
+      <c r="Q31" s="17"/>
+      <c r="R31" s="17"/>
+      <c r="S31" s="17"/>
+      <c r="T31" s="18"/>
+      <c r="U31" s="16"/>
+      <c r="V31" s="17"/>
+      <c r="W31" s="17"/>
+      <c r="X31" s="18"/>
+    </row>
+    <row r="32" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A32" s="15"/>
+      <c r="B32" s="16"/>
+      <c r="C32" s="17"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="16"/>
+      <c r="G32" s="17"/>
+      <c r="H32" s="17"/>
+      <c r="I32" s="17"/>
+      <c r="J32" s="17"/>
+      <c r="K32" s="17"/>
+      <c r="L32" s="18"/>
+      <c r="M32" s="16"/>
+      <c r="N32" s="17"/>
+      <c r="O32" s="17"/>
+      <c r="P32" s="17"/>
+      <c r="Q32" s="17"/>
+      <c r="R32" s="17"/>
+      <c r="S32" s="17"/>
+      <c r="T32" s="18"/>
+      <c r="U32" s="16"/>
+      <c r="V32" s="17"/>
+      <c r="W32" s="17"/>
+      <c r="X32" s="18"/>
+    </row>
+    <row r="33" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A33" s="15"/>
+      <c r="B33" s="16"/>
+      <c r="C33" s="17"/>
+      <c r="D33" s="17"/>
+      <c r="E33" s="18"/>
+      <c r="F33" s="16"/>
+      <c r="G33" s="17"/>
+      <c r="H33" s="17"/>
+      <c r="I33" s="17"/>
+      <c r="J33" s="17"/>
+      <c r="K33" s="17"/>
+      <c r="L33" s="18"/>
+      <c r="M33" s="16"/>
+      <c r="N33" s="17"/>
+      <c r="O33" s="17"/>
+      <c r="P33" s="17"/>
+      <c r="Q33" s="17"/>
+      <c r="R33" s="17"/>
+      <c r="S33" s="17"/>
+      <c r="T33" s="18"/>
+      <c r="U33" s="16"/>
+      <c r="V33" s="17"/>
+      <c r="W33" s="17"/>
+      <c r="X33" s="18"/>
+    </row>
+    <row r="34" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A34" s="15"/>
+      <c r="B34" s="16"/>
+      <c r="C34" s="17"/>
+      <c r="D34" s="17"/>
+      <c r="E34" s="18"/>
+      <c r="F34" s="16"/>
+      <c r="G34" s="17"/>
+      <c r="H34" s="17"/>
+      <c r="I34" s="17"/>
+      <c r="J34" s="17"/>
+      <c r="K34" s="17"/>
+      <c r="L34" s="18"/>
+      <c r="M34" s="16"/>
+      <c r="N34" s="17"/>
+      <c r="O34" s="17"/>
+      <c r="P34" s="17"/>
+      <c r="Q34" s="17"/>
+      <c r="R34" s="17"/>
+      <c r="S34" s="17"/>
+      <c r="T34" s="18"/>
+      <c r="U34" s="16"/>
+      <c r="V34" s="17"/>
+      <c r="W34" s="17"/>
+      <c r="X34" s="18"/>
+    </row>
+    <row r="35" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A35" s="15"/>
+      <c r="B35" s="16"/>
+      <c r="C35" s="17"/>
+      <c r="D35" s="17"/>
+      <c r="E35" s="18"/>
+      <c r="F35" s="16"/>
+      <c r="G35" s="17"/>
+      <c r="H35" s="17"/>
+      <c r="I35" s="17"/>
+      <c r="J35" s="17"/>
+      <c r="K35" s="17"/>
+      <c r="L35" s="18"/>
+      <c r="M35" s="16"/>
+      <c r="N35" s="17"/>
+      <c r="O35" s="17"/>
+      <c r="P35" s="17"/>
+      <c r="Q35" s="17"/>
+      <c r="R35" s="17"/>
+      <c r="S35" s="17"/>
+      <c r="T35" s="18"/>
+      <c r="U35" s="16"/>
+      <c r="V35" s="17"/>
+      <c r="W35" s="17"/>
+      <c r="X35" s="18"/>
+    </row>
+    <row r="36" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A36" s="15"/>
+      <c r="B36" s="16"/>
+      <c r="C36" s="17"/>
+      <c r="D36" s="17"/>
+      <c r="E36" s="18"/>
+      <c r="F36" s="16"/>
+      <c r="G36" s="17"/>
+      <c r="H36" s="17"/>
+      <c r="I36" s="17"/>
+      <c r="J36" s="17"/>
+      <c r="K36" s="17"/>
+      <c r="L36" s="18"/>
+      <c r="M36" s="16"/>
+      <c r="N36" s="17"/>
+      <c r="O36" s="17"/>
+      <c r="P36" s="17"/>
+      <c r="Q36" s="17"/>
+      <c r="R36" s="17"/>
+      <c r="S36" s="17"/>
+      <c r="T36" s="18"/>
+      <c r="U36" s="16"/>
+      <c r="V36" s="17"/>
+      <c r="W36" s="17"/>
+      <c r="X36" s="18"/>
+    </row>
+    <row r="37" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A37" s="15"/>
+      <c r="B37" s="16"/>
+      <c r="C37" s="17"/>
+      <c r="D37" s="17"/>
+      <c r="E37" s="18"/>
+      <c r="F37" s="16"/>
+      <c r="G37" s="17"/>
+      <c r="H37" s="17"/>
+      <c r="I37" s="17"/>
+      <c r="J37" s="17"/>
+      <c r="K37" s="17"/>
+      <c r="L37" s="18"/>
+      <c r="M37" s="16"/>
+      <c r="N37" s="17"/>
+      <c r="O37" s="17"/>
+      <c r="P37" s="17"/>
+      <c r="Q37" s="17"/>
+      <c r="R37" s="17"/>
+      <c r="S37" s="17"/>
+      <c r="T37" s="18"/>
+      <c r="U37" s="16"/>
+      <c r="V37" s="17"/>
+      <c r="W37" s="17"/>
+      <c r="X37" s="18"/>
+    </row>
+    <row r="38" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A38" s="15"/>
+      <c r="B38" s="16"/>
+      <c r="C38" s="17"/>
+      <c r="D38" s="17"/>
+      <c r="E38" s="18"/>
+      <c r="F38" s="16"/>
+      <c r="G38" s="17"/>
+      <c r="H38" s="17"/>
+      <c r="I38" s="17"/>
+      <c r="J38" s="17"/>
+      <c r="K38" s="17"/>
+      <c r="L38" s="18"/>
+      <c r="M38" s="16"/>
+      <c r="N38" s="17"/>
+      <c r="O38" s="17"/>
+      <c r="P38" s="17"/>
+      <c r="Q38" s="17"/>
+      <c r="R38" s="17"/>
+      <c r="S38" s="17"/>
+      <c r="T38" s="18"/>
+      <c r="U38" s="16"/>
+      <c r="V38" s="17"/>
+      <c r="W38" s="17"/>
+      <c r="X38" s="18"/>
+    </row>
+    <row r="39" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A39" s="15"/>
+      <c r="B39" s="16"/>
+      <c r="C39" s="17"/>
+      <c r="D39" s="17"/>
+      <c r="E39" s="18"/>
+      <c r="F39" s="16"/>
+      <c r="G39" s="17"/>
+      <c r="H39" s="17"/>
+      <c r="I39" s="17"/>
+      <c r="J39" s="17"/>
+      <c r="K39" s="17"/>
+      <c r="L39" s="18"/>
+      <c r="M39" s="16"/>
+      <c r="N39" s="17"/>
+      <c r="O39" s="17"/>
+      <c r="P39" s="17"/>
+      <c r="Q39" s="17"/>
+      <c r="R39" s="17"/>
+      <c r="S39" s="17"/>
+      <c r="T39" s="18"/>
+      <c r="U39" s="16"/>
+      <c r="V39" s="17"/>
+      <c r="W39" s="17"/>
+      <c r="X39" s="18"/>
+    </row>
+    <row r="40" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A40" s="15"/>
+      <c r="B40" s="16"/>
+      <c r="C40" s="17"/>
+      <c r="D40" s="17"/>
+      <c r="E40" s="18"/>
+      <c r="F40" s="16"/>
+      <c r="G40" s="17"/>
+      <c r="H40" s="17"/>
+      <c r="I40" s="17"/>
+      <c r="J40" s="17"/>
+      <c r="K40" s="17"/>
+      <c r="L40" s="18"/>
+      <c r="M40" s="16"/>
+      <c r="N40" s="17"/>
+      <c r="O40" s="17"/>
+      <c r="P40" s="17"/>
+      <c r="Q40" s="17"/>
+      <c r="R40" s="17"/>
+      <c r="S40" s="17"/>
+      <c r="T40" s="18"/>
+      <c r="U40" s="16"/>
+      <c r="V40" s="17"/>
+      <c r="W40" s="17"/>
+      <c r="X40" s="18"/>
+    </row>
+    <row r="41" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A41" s="15"/>
+      <c r="B41" s="16"/>
+      <c r="C41" s="17"/>
+      <c r="D41" s="17"/>
+      <c r="E41" s="18"/>
+      <c r="F41" s="16"/>
+      <c r="G41" s="17"/>
+      <c r="H41" s="17"/>
+      <c r="I41" s="17"/>
+      <c r="J41" s="17"/>
+      <c r="K41" s="17"/>
+      <c r="L41" s="18"/>
+      <c r="M41" s="16"/>
+      <c r="N41" s="17"/>
+      <c r="O41" s="17"/>
+      <c r="P41" s="17"/>
+      <c r="Q41" s="17"/>
+      <c r="R41" s="17"/>
+      <c r="S41" s="17"/>
+      <c r="T41" s="18"/>
+      <c r="U41" s="16"/>
+      <c r="V41" s="17"/>
+      <c r="W41" s="17"/>
+      <c r="X41" s="18"/>
+    </row>
+    <row r="42" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A42" s="15"/>
+      <c r="B42" s="16"/>
+      <c r="C42" s="17"/>
+      <c r="D42" s="17"/>
+      <c r="E42" s="18"/>
+      <c r="F42" s="16"/>
+      <c r="G42" s="17"/>
+      <c r="H42" s="17"/>
+      <c r="I42" s="17"/>
+      <c r="J42" s="17"/>
+      <c r="K42" s="17"/>
+      <c r="L42" s="18"/>
+      <c r="M42" s="16"/>
+      <c r="N42" s="17"/>
+      <c r="O42" s="17"/>
+      <c r="P42" s="17"/>
+      <c r="Q42" s="17"/>
+      <c r="R42" s="17"/>
+      <c r="S42" s="17"/>
+      <c r="T42" s="18"/>
+      <c r="U42" s="16"/>
+      <c r="V42" s="17"/>
+      <c r="W42" s="17"/>
+      <c r="X42" s="18"/>
+    </row>
+    <row r="43" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A43" s="15"/>
+      <c r="B43" s="16"/>
+      <c r="C43" s="17"/>
+      <c r="D43" s="17"/>
+      <c r="E43" s="18"/>
+      <c r="F43" s="16"/>
+      <c r="G43" s="17"/>
+      <c r="H43" s="17"/>
+      <c r="I43" s="17"/>
+      <c r="J43" s="17"/>
+      <c r="K43" s="17"/>
+      <c r="L43" s="18"/>
+      <c r="M43" s="16"/>
+      <c r="N43" s="17"/>
+      <c r="O43" s="17"/>
+      <c r="P43" s="17"/>
+      <c r="Q43" s="17"/>
+      <c r="R43" s="17"/>
+      <c r="S43" s="17"/>
+      <c r="T43" s="18"/>
+      <c r="U43" s="16"/>
+      <c r="V43" s="17"/>
+      <c r="W43" s="17"/>
+      <c r="X43" s="18"/>
+    </row>
+    <row r="44" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A44" s="15"/>
+      <c r="B44" s="16"/>
+      <c r="C44" s="17"/>
+      <c r="D44" s="17"/>
+      <c r="E44" s="18"/>
+      <c r="F44" s="16"/>
+      <c r="G44" s="17"/>
+      <c r="H44" s="17"/>
+      <c r="I44" s="17"/>
+      <c r="J44" s="17"/>
+      <c r="K44" s="17"/>
+      <c r="L44" s="18"/>
+      <c r="M44" s="16"/>
+      <c r="N44" s="17"/>
+      <c r="O44" s="17"/>
+      <c r="P44" s="17"/>
+      <c r="Q44" s="17"/>
+      <c r="R44" s="17"/>
+      <c r="S44" s="17"/>
+      <c r="T44" s="18"/>
+      <c r="U44" s="16"/>
+      <c r="V44" s="17"/>
+      <c r="W44" s="17"/>
+      <c r="X44" s="18"/>
+    </row>
+    <row r="45" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A45" s="15"/>
+      <c r="B45" s="16"/>
+      <c r="C45" s="17"/>
+      <c r="D45" s="17"/>
+      <c r="E45" s="18"/>
+      <c r="F45" s="16"/>
+      <c r="G45" s="17"/>
+      <c r="H45" s="17"/>
+      <c r="I45" s="17"/>
+      <c r="J45" s="17"/>
+      <c r="K45" s="17"/>
+      <c r="L45" s="18"/>
+      <c r="M45" s="16"/>
+      <c r="N45" s="17"/>
+      <c r="O45" s="17"/>
+      <c r="P45" s="17"/>
+      <c r="Q45" s="17"/>
+      <c r="R45" s="17"/>
+      <c r="S45" s="17"/>
+      <c r="T45" s="18"/>
+      <c r="U45" s="16"/>
+      <c r="V45" s="17"/>
+      <c r="W45" s="17"/>
+      <c r="X45" s="18"/>
+    </row>
+    <row r="46" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A46" s="15"/>
+      <c r="B46" s="16"/>
+      <c r="C46" s="17"/>
+      <c r="D46" s="17"/>
+      <c r="E46" s="18"/>
+      <c r="F46" s="16"/>
+      <c r="G46" s="17"/>
+      <c r="H46" s="17"/>
+      <c r="I46" s="17"/>
+      <c r="J46" s="17"/>
+      <c r="K46" s="17"/>
+      <c r="L46" s="18"/>
+      <c r="M46" s="16"/>
+      <c r="N46" s="17"/>
+      <c r="O46" s="17"/>
+      <c r="P46" s="17"/>
+      <c r="Q46" s="17"/>
+      <c r="R46" s="17"/>
+      <c r="S46" s="17"/>
+      <c r="T46" s="18"/>
+      <c r="U46" s="16"/>
+      <c r="V46" s="17"/>
+      <c r="W46" s="17"/>
+      <c r="X46" s="18"/>
+    </row>
+    <row r="47" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A47" s="15"/>
+      <c r="B47" s="16"/>
+      <c r="C47" s="17"/>
+      <c r="D47" s="17"/>
+      <c r="E47" s="18"/>
+      <c r="F47" s="16"/>
+      <c r="G47" s="17"/>
+      <c r="H47" s="17"/>
+      <c r="I47" s="17"/>
+      <c r="J47" s="17"/>
+      <c r="K47" s="17"/>
+      <c r="L47" s="18"/>
+      <c r="M47" s="16"/>
+      <c r="N47" s="17"/>
+      <c r="O47" s="17"/>
+      <c r="P47" s="17"/>
+      <c r="Q47" s="17"/>
+      <c r="R47" s="17"/>
+      <c r="S47" s="17"/>
+      <c r="T47" s="18"/>
+      <c r="U47" s="16"/>
+      <c r="V47" s="17"/>
+      <c r="W47" s="17"/>
+      <c r="X47" s="18"/>
+    </row>
+    <row r="48" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A48" s="15"/>
+      <c r="B48" s="16"/>
+      <c r="C48" s="17"/>
+      <c r="D48" s="17"/>
+      <c r="E48" s="18"/>
+      <c r="F48" s="16"/>
+      <c r="G48" s="17"/>
+      <c r="H48" s="17"/>
+      <c r="I48" s="17"/>
+      <c r="J48" s="17"/>
+      <c r="K48" s="17"/>
+      <c r="L48" s="18"/>
+      <c r="M48" s="16"/>
+      <c r="N48" s="17"/>
+      <c r="O48" s="17"/>
+      <c r="P48" s="17"/>
+      <c r="Q48" s="17"/>
+      <c r="R48" s="17"/>
+      <c r="S48" s="17"/>
+      <c r="T48" s="18"/>
+      <c r="U48" s="16"/>
+      <c r="V48" s="17"/>
+      <c r="W48" s="17"/>
+      <c r="X48" s="18"/>
+    </row>
+    <row r="49" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A49" s="15"/>
+      <c r="B49" s="16"/>
+      <c r="C49" s="17"/>
+      <c r="D49" s="17"/>
+      <c r="E49" s="18"/>
+      <c r="F49" s="16"/>
+      <c r="G49" s="17"/>
+      <c r="H49" s="17"/>
+      <c r="I49" s="17"/>
+      <c r="J49" s="17"/>
+      <c r="K49" s="17"/>
+      <c r="L49" s="18"/>
+      <c r="M49" s="16"/>
+      <c r="N49" s="17"/>
+      <c r="O49" s="17"/>
+      <c r="P49" s="17"/>
+      <c r="Q49" s="17"/>
+      <c r="R49" s="17"/>
+      <c r="S49" s="17"/>
+      <c r="T49" s="18"/>
+      <c r="U49" s="16"/>
+      <c r="V49" s="17"/>
+      <c r="W49" s="17"/>
+      <c r="X49" s="18"/>
+    </row>
+    <row r="50" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A50" s="15"/>
+      <c r="B50" s="16"/>
+      <c r="C50" s="17"/>
+      <c r="D50" s="17"/>
+      <c r="E50" s="18"/>
+      <c r="F50" s="16"/>
+      <c r="G50" s="17"/>
+      <c r="H50" s="17"/>
+      <c r="I50" s="17"/>
+      <c r="J50" s="17"/>
+      <c r="K50" s="17"/>
+      <c r="L50" s="18"/>
+      <c r="M50" s="16"/>
+      <c r="N50" s="17"/>
+      <c r="O50" s="17"/>
+      <c r="P50" s="17"/>
+      <c r="Q50" s="17"/>
+      <c r="R50" s="17"/>
+      <c r="S50" s="17"/>
+      <c r="T50" s="18"/>
+      <c r="U50" s="16"/>
+      <c r="V50" s="17"/>
+      <c r="W50" s="17"/>
+      <c r="X50" s="18"/>
+    </row>
+    <row r="51" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A51" s="15"/>
+      <c r="B51" s="16"/>
+      <c r="C51" s="17"/>
+      <c r="D51" s="17"/>
+      <c r="E51" s="18"/>
+      <c r="F51" s="16"/>
+      <c r="G51" s="17"/>
+      <c r="H51" s="17"/>
+      <c r="I51" s="17"/>
+      <c r="J51" s="17"/>
+      <c r="K51" s="17"/>
+      <c r="L51" s="18"/>
+      <c r="M51" s="16"/>
+      <c r="N51" s="17"/>
+      <c r="O51" s="17"/>
+      <c r="P51" s="17"/>
+      <c r="Q51" s="17"/>
+      <c r="R51" s="17"/>
+      <c r="S51" s="17"/>
+      <c r="T51" s="18"/>
+      <c r="U51" s="16"/>
+      <c r="V51" s="17"/>
+      <c r="W51" s="17"/>
+      <c r="X51" s="18"/>
+    </row>
+    <row r="52" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="23"/>
+      <c r="B52" s="24"/>
+      <c r="C52" s="25"/>
+      <c r="D52" s="25"/>
+      <c r="E52" s="26"/>
+      <c r="F52" s="24"/>
+      <c r="G52" s="25"/>
+      <c r="H52" s="25"/>
+      <c r="I52" s="25"/>
+      <c r="J52" s="25"/>
+      <c r="K52" s="25"/>
+      <c r="L52" s="26"/>
+      <c r="M52" s="24"/>
+      <c r="N52" s="25"/>
+      <c r="O52" s="25"/>
+      <c r="P52" s="25"/>
+      <c r="Q52" s="25"/>
+      <c r="R52" s="25"/>
+      <c r="S52" s="25"/>
+      <c r="T52" s="26"/>
+      <c r="U52" s="24"/>
+      <c r="V52" s="25"/>
+      <c r="W52" s="25"/>
+      <c r="X52" s="26"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="F1:L1"/>
+    <mergeCell ref="M1:T1"/>
+    <mergeCell ref="U1:X1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/inst/Instructions.xlsx
+++ b/inst/Instructions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/martics/Documents/GitHub/PhenotypeR/inst/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A15D251C-2F7C-BF4D-A38A-CE408E5C273D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2412D5ED-E7BD-2245-996B-4B3B8ECF28C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17420" activeTab="1" xr2:uid="{CDA5D9F4-215A-E946-86DB-1C84C02DBC91}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t>Overview</t>
   </si>
@@ -609,9 +609,6 @@
       </rPr>
       <t xml:space="preserve"> Fill in the columns. Missing (unpopulated) values will be interpreted as using the defaults as populated by the different functions in PhenotypeR.</t>
     </r>
-  </si>
-  <si>
-    <t>abc</t>
   </si>
 </sst>
 </file>
@@ -1668,9 +1665,7 @@
       </c>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A3" s="19" t="s">
-        <v>42</v>
-      </c>
+      <c r="A3" s="19"/>
       <c r="B3" s="20"/>
       <c r="C3" s="21"/>
       <c r="D3" s="21"/>

--- a/inst/Instructions.xlsx
+++ b/inst/Instructions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/martics/Documents/GitHub/PhenotypeR/inst/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2412D5ED-E7BD-2245-996B-4B3B8ECF28C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87FD8508-A573-B34F-AE4C-FE22327D1CCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17420" activeTab="1" xr2:uid="{CDA5D9F4-215A-E946-86DB-1C84C02DBC91}"/>
   </bookViews>
@@ -36,6 +36,49 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>martics</author>
+  </authors>
+  <commentList>
+    <comment ref="X2" authorId="0" shapeId="0" xr:uid="{BB738428-690C-DF4C-8F11-D4CCC9AA51DB}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>martics:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Aptos Narrow"/>
+          </rPr>
+          <t xml:space="preserve">Use NA to only specify one boundary: 2000-01-01 to NA (this would subset the incidence and/or prevalence to from 2000 onwards with no upper bound)
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
@@ -565,20 +608,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Date Range
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="2" tint="-0.499984740745262"/>
-        <rFont val="Aptos Narrow (Body)"/>
-      </rPr>
-      <t>(Study period start/ Study period end)</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">Snapshot
 </t>
     </r>
@@ -608,6 +637,20 @@
         <rFont val="Aptos Narrow"/>
       </rPr>
       <t xml:space="preserve"> Fill in the columns. Missing (unpopulated) values will be interpreted as using the defaults as populated by the different functions in PhenotypeR.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Date Range
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="2" tint="-0.499984740745262"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t>(YYYY-MM-DD to YYYY-MM-DD)</t>
     </r>
   </si>
 </sst>
@@ -615,7 +658,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -705,6 +748,24 @@
       <sz val="14"/>
       <color theme="2" tint="-0.499984740745262"/>
       <name val="Aptos Narrow (Body)"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1524,7 +1585,7 @@
     </row>
     <row r="14" spans="1:1" ht="34" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16" spans="1:1" ht="25" x14ac:dyDescent="0.3">
@@ -1548,7 +1609,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66189217-AFFF-FF4C-96F8-B7D661B6748A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66189217-AFFF-FF4C-96F8-B7D661B6748A}">
   <dimension ref="A1:X52"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -1595,7 +1656,7 @@
     <row r="2" spans="1:24" ht="101" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="28"/>
       <c r="B2" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C2" s="12" t="s">
         <v>18</v>
@@ -1661,7 +1722,7 @@
         <v>38</v>
       </c>
       <c r="X2" s="10" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.2">
@@ -2973,5 +3034,6 @@
     <mergeCell ref="U1:X1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/inst/Instructions.xlsx
+++ b/inst/Instructions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/martics/Documents/GitHub/PhenotypeR/inst/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87FD8508-A573-B34F-AE4C-FE22327D1CCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A00848E-D255-BC47-99A5-076D8A3BE1A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17420" activeTab="1" xr2:uid="{CDA5D9F4-215A-E946-86DB-1C84C02DBC91}"/>
   </bookViews>
@@ -42,7 +42,7 @@
     <author>martics</author>
   </authors>
   <commentList>
-    <comment ref="X2" authorId="0" shapeId="0" xr:uid="{BB738428-690C-DF4C-8F11-D4CCC9AA51DB}">
+    <comment ref="W2" authorId="0" shapeId="0" xr:uid="{BB738428-690C-DF4C-8F11-D4CCC9AA51DB}">
       <text>
         <r>
           <rPr>
@@ -80,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t>Overview</t>
   </si>
@@ -511,20 +511,6 @@
   <si>
     <r>
       <t xml:space="preserve">Cohort Survival
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="2" tint="-0.499984740745262"/>
-        <rFont val="Aptos Narrow (Body)"/>
-      </rPr>
-      <t>(TRUE/FALSE)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Cohort overlap
 </t>
     </r>
     <r>
@@ -1585,7 +1571,7 @@
     </row>
     <row r="14" spans="1:1" ht="34" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:1" ht="25" x14ac:dyDescent="0.3">
@@ -1610,14 +1596,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66189217-AFFF-FF4C-96F8-B7D661B6748A}">
-  <dimension ref="A1:X52"/>
+  <dimension ref="A1:W52"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="27.83203125" customWidth="1"/>
-    <col min="2" max="24" width="14" customWidth="1"/>
+    <col min="2" max="23" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:23" ht="25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="27" t="s">
         <v>13</v>
       </c>
@@ -1644,19 +1630,18 @@
       <c r="P1" s="33"/>
       <c r="Q1" s="33"/>
       <c r="R1" s="33"/>
-      <c r="S1" s="33"/>
-      <c r="T1" s="34"/>
-      <c r="U1" s="29" t="s">
+      <c r="S1" s="34"/>
+      <c r="T1" s="29" t="s">
         <v>17</v>
       </c>
+      <c r="U1" s="30"/>
       <c r="V1" s="30"/>
-      <c r="W1" s="30"/>
-      <c r="X1" s="31"/>
-    </row>
-    <row r="2" spans="1:24" ht="101" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="W1" s="31"/>
+    </row>
+    <row r="2" spans="1:23" ht="101" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="28"/>
       <c r="B2" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C2" s="12" t="s">
         <v>18</v>
@@ -1706,26 +1691,23 @@
       <c r="R2" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="S2" s="8" t="s">
+      <c r="S2" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="T2" s="10" t="s">
+      <c r="T2" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="U2" s="7" t="s">
+      <c r="U2" s="8" t="s">
         <v>36</v>
       </c>
       <c r="V2" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="W2" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="X2" s="10" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="W2" s="10" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A3" s="19"/>
       <c r="B3" s="20"/>
       <c r="C3" s="21"/>
@@ -1744,14 +1726,13 @@
       <c r="P3" s="21"/>
       <c r="Q3" s="21"/>
       <c r="R3" s="21"/>
-      <c r="S3" s="21"/>
-      <c r="T3" s="22"/>
-      <c r="U3" s="20"/>
+      <c r="S3" s="22"/>
+      <c r="T3" s="20"/>
+      <c r="U3" s="21"/>
       <c r="V3" s="21"/>
-      <c r="W3" s="21"/>
-      <c r="X3" s="22"/>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="W3" s="22"/>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A4" s="15"/>
       <c r="B4" s="16"/>
       <c r="C4" s="17"/>
@@ -1770,14 +1751,13 @@
       <c r="P4" s="17"/>
       <c r="Q4" s="17"/>
       <c r="R4" s="17"/>
-      <c r="S4" s="17"/>
-      <c r="T4" s="18"/>
-      <c r="U4" s="16"/>
+      <c r="S4" s="18"/>
+      <c r="T4" s="16"/>
+      <c r="U4" s="17"/>
       <c r="V4" s="17"/>
-      <c r="W4" s="17"/>
-      <c r="X4" s="18"/>
-    </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="W4" s="18"/>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="15"/>
       <c r="B5" s="16"/>
       <c r="C5" s="17"/>
@@ -1796,14 +1776,13 @@
       <c r="P5" s="17"/>
       <c r="Q5" s="17"/>
       <c r="R5" s="17"/>
-      <c r="S5" s="17"/>
-      <c r="T5" s="18"/>
-      <c r="U5" s="16"/>
+      <c r="S5" s="18"/>
+      <c r="T5" s="16"/>
+      <c r="U5" s="17"/>
       <c r="V5" s="17"/>
-      <c r="W5" s="17"/>
-      <c r="X5" s="18"/>
-    </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="W5" s="18"/>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A6" s="15"/>
       <c r="B6" s="16"/>
       <c r="C6" s="17"/>
@@ -1822,14 +1801,13 @@
       <c r="P6" s="17"/>
       <c r="Q6" s="17"/>
       <c r="R6" s="17"/>
-      <c r="S6" s="17"/>
-      <c r="T6" s="18"/>
-      <c r="U6" s="16"/>
+      <c r="S6" s="18"/>
+      <c r="T6" s="16"/>
+      <c r="U6" s="17"/>
       <c r="V6" s="17"/>
-      <c r="W6" s="17"/>
-      <c r="X6" s="18"/>
-    </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="W6" s="18"/>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A7" s="15"/>
       <c r="B7" s="16"/>
       <c r="C7" s="17"/>
@@ -1848,14 +1826,13 @@
       <c r="P7" s="17"/>
       <c r="Q7" s="17"/>
       <c r="R7" s="17"/>
-      <c r="S7" s="17"/>
-      <c r="T7" s="18"/>
-      <c r="U7" s="16"/>
+      <c r="S7" s="18"/>
+      <c r="T7" s="16"/>
+      <c r="U7" s="17"/>
       <c r="V7" s="17"/>
-      <c r="W7" s="17"/>
-      <c r="X7" s="18"/>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="W7" s="18"/>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A8" s="15"/>
       <c r="B8" s="16"/>
       <c r="C8" s="17"/>
@@ -1874,14 +1851,13 @@
       <c r="P8" s="17"/>
       <c r="Q8" s="17"/>
       <c r="R8" s="17"/>
-      <c r="S8" s="17"/>
-      <c r="T8" s="18"/>
-      <c r="U8" s="16"/>
+      <c r="S8" s="18"/>
+      <c r="T8" s="16"/>
+      <c r="U8" s="17"/>
       <c r="V8" s="17"/>
-      <c r="W8" s="17"/>
-      <c r="X8" s="18"/>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="W8" s="18"/>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A9" s="15"/>
       <c r="B9" s="16"/>
       <c r="C9" s="17"/>
@@ -1900,14 +1876,13 @@
       <c r="P9" s="17"/>
       <c r="Q9" s="17"/>
       <c r="R9" s="17"/>
-      <c r="S9" s="17"/>
-      <c r="T9" s="18"/>
-      <c r="U9" s="16"/>
+      <c r="S9" s="18"/>
+      <c r="T9" s="16"/>
+      <c r="U9" s="17"/>
       <c r="V9" s="17"/>
-      <c r="W9" s="17"/>
-      <c r="X9" s="18"/>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="W9" s="18"/>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A10" s="15"/>
       <c r="B10" s="16"/>
       <c r="C10" s="17"/>
@@ -1926,14 +1901,13 @@
       <c r="P10" s="17"/>
       <c r="Q10" s="17"/>
       <c r="R10" s="17"/>
-      <c r="S10" s="17"/>
-      <c r="T10" s="18"/>
-      <c r="U10" s="16"/>
+      <c r="S10" s="18"/>
+      <c r="T10" s="16"/>
+      <c r="U10" s="17"/>
       <c r="V10" s="17"/>
-      <c r="W10" s="17"/>
-      <c r="X10" s="18"/>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="W10" s="18"/>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A11" s="15"/>
       <c r="B11" s="16"/>
       <c r="C11" s="17"/>
@@ -1952,14 +1926,13 @@
       <c r="P11" s="17"/>
       <c r="Q11" s="17"/>
       <c r="R11" s="17"/>
-      <c r="S11" s="17"/>
-      <c r="T11" s="18"/>
-      <c r="U11" s="16"/>
+      <c r="S11" s="18"/>
+      <c r="T11" s="16"/>
+      <c r="U11" s="17"/>
       <c r="V11" s="17"/>
-      <c r="W11" s="17"/>
-      <c r="X11" s="18"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="W11" s="18"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A12" s="15"/>
       <c r="B12" s="16"/>
       <c r="C12" s="17"/>
@@ -1978,14 +1951,13 @@
       <c r="P12" s="17"/>
       <c r="Q12" s="17"/>
       <c r="R12" s="17"/>
-      <c r="S12" s="17"/>
-      <c r="T12" s="18"/>
-      <c r="U12" s="16"/>
+      <c r="S12" s="18"/>
+      <c r="T12" s="16"/>
+      <c r="U12" s="17"/>
       <c r="V12" s="17"/>
-      <c r="W12" s="17"/>
-      <c r="X12" s="18"/>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="W12" s="18"/>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A13" s="15"/>
       <c r="B13" s="16"/>
       <c r="C13" s="17"/>
@@ -2004,14 +1976,13 @@
       <c r="P13" s="17"/>
       <c r="Q13" s="17"/>
       <c r="R13" s="17"/>
-      <c r="S13" s="17"/>
-      <c r="T13" s="18"/>
-      <c r="U13" s="16"/>
+      <c r="S13" s="18"/>
+      <c r="T13" s="16"/>
+      <c r="U13" s="17"/>
       <c r="V13" s="17"/>
-      <c r="W13" s="17"/>
-      <c r="X13" s="18"/>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="W13" s="18"/>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A14" s="15"/>
       <c r="B14" s="16"/>
       <c r="C14" s="17"/>
@@ -2030,14 +2001,13 @@
       <c r="P14" s="17"/>
       <c r="Q14" s="17"/>
       <c r="R14" s="17"/>
-      <c r="S14" s="17"/>
-      <c r="T14" s="18"/>
-      <c r="U14" s="16"/>
+      <c r="S14" s="18"/>
+      <c r="T14" s="16"/>
+      <c r="U14" s="17"/>
       <c r="V14" s="17"/>
-      <c r="W14" s="17"/>
-      <c r="X14" s="18"/>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="W14" s="18"/>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A15" s="15"/>
       <c r="B15" s="16"/>
       <c r="C15" s="17"/>
@@ -2056,14 +2026,13 @@
       <c r="P15" s="17"/>
       <c r="Q15" s="17"/>
       <c r="R15" s="17"/>
-      <c r="S15" s="17"/>
-      <c r="T15" s="18"/>
-      <c r="U15" s="16"/>
+      <c r="S15" s="18"/>
+      <c r="T15" s="16"/>
+      <c r="U15" s="17"/>
       <c r="V15" s="17"/>
-      <c r="W15" s="17"/>
-      <c r="X15" s="18"/>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="W15" s="18"/>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A16" s="15"/>
       <c r="B16" s="16"/>
       <c r="C16" s="17"/>
@@ -2082,14 +2051,13 @@
       <c r="P16" s="17"/>
       <c r="Q16" s="17"/>
       <c r="R16" s="17"/>
-      <c r="S16" s="17"/>
-      <c r="T16" s="18"/>
-      <c r="U16" s="16"/>
+      <c r="S16" s="18"/>
+      <c r="T16" s="16"/>
+      <c r="U16" s="17"/>
       <c r="V16" s="17"/>
-      <c r="W16" s="17"/>
-      <c r="X16" s="18"/>
-    </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="W16" s="18"/>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A17" s="15"/>
       <c r="B17" s="16"/>
       <c r="C17" s="17"/>
@@ -2108,14 +2076,13 @@
       <c r="P17" s="17"/>
       <c r="Q17" s="17"/>
       <c r="R17" s="17"/>
-      <c r="S17" s="17"/>
-      <c r="T17" s="18"/>
-      <c r="U17" s="16"/>
+      <c r="S17" s="18"/>
+      <c r="T17" s="16"/>
+      <c r="U17" s="17"/>
       <c r="V17" s="17"/>
-      <c r="W17" s="17"/>
-      <c r="X17" s="18"/>
-    </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="W17" s="18"/>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A18" s="15"/>
       <c r="B18" s="16"/>
       <c r="C18" s="17"/>
@@ -2134,14 +2101,13 @@
       <c r="P18" s="17"/>
       <c r="Q18" s="17"/>
       <c r="R18" s="17"/>
-      <c r="S18" s="17"/>
-      <c r="T18" s="18"/>
-      <c r="U18" s="16"/>
+      <c r="S18" s="18"/>
+      <c r="T18" s="16"/>
+      <c r="U18" s="17"/>
       <c r="V18" s="17"/>
-      <c r="W18" s="17"/>
-      <c r="X18" s="18"/>
-    </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="W18" s="18"/>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A19" s="15"/>
       <c r="B19" s="16"/>
       <c r="C19" s="17"/>
@@ -2160,14 +2126,13 @@
       <c r="P19" s="17"/>
       <c r="Q19" s="17"/>
       <c r="R19" s="17"/>
-      <c r="S19" s="17"/>
-      <c r="T19" s="18"/>
-      <c r="U19" s="16"/>
+      <c r="S19" s="18"/>
+      <c r="T19" s="16"/>
+      <c r="U19" s="17"/>
       <c r="V19" s="17"/>
-      <c r="W19" s="17"/>
-      <c r="X19" s="18"/>
-    </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="W19" s="18"/>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A20" s="15"/>
       <c r="B20" s="16"/>
       <c r="C20" s="17"/>
@@ -2186,14 +2151,13 @@
       <c r="P20" s="17"/>
       <c r="Q20" s="17"/>
       <c r="R20" s="17"/>
-      <c r="S20" s="17"/>
-      <c r="T20" s="18"/>
-      <c r="U20" s="16"/>
+      <c r="S20" s="18"/>
+      <c r="T20" s="16"/>
+      <c r="U20" s="17"/>
       <c r="V20" s="17"/>
-      <c r="W20" s="17"/>
-      <c r="X20" s="18"/>
-    </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="W20" s="18"/>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A21" s="15"/>
       <c r="B21" s="16"/>
       <c r="C21" s="17"/>
@@ -2212,14 +2176,13 @@
       <c r="P21" s="17"/>
       <c r="Q21" s="17"/>
       <c r="R21" s="17"/>
-      <c r="S21" s="17"/>
-      <c r="T21" s="18"/>
-      <c r="U21" s="16"/>
+      <c r="S21" s="18"/>
+      <c r="T21" s="16"/>
+      <c r="U21" s="17"/>
       <c r="V21" s="17"/>
-      <c r="W21" s="17"/>
-      <c r="X21" s="18"/>
-    </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="W21" s="18"/>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A22" s="15"/>
       <c r="B22" s="16"/>
       <c r="C22" s="17"/>
@@ -2238,14 +2201,13 @@
       <c r="P22" s="17"/>
       <c r="Q22" s="17"/>
       <c r="R22" s="17"/>
-      <c r="S22" s="17"/>
-      <c r="T22" s="18"/>
-      <c r="U22" s="16"/>
+      <c r="S22" s="18"/>
+      <c r="T22" s="16"/>
+      <c r="U22" s="17"/>
       <c r="V22" s="17"/>
-      <c r="W22" s="17"/>
-      <c r="X22" s="18"/>
-    </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="W22" s="18"/>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A23" s="15"/>
       <c r="B23" s="16"/>
       <c r="C23" s="17"/>
@@ -2264,14 +2226,13 @@
       <c r="P23" s="17"/>
       <c r="Q23" s="17"/>
       <c r="R23" s="17"/>
-      <c r="S23" s="17"/>
-      <c r="T23" s="18"/>
-      <c r="U23" s="16"/>
+      <c r="S23" s="18"/>
+      <c r="T23" s="16"/>
+      <c r="U23" s="17"/>
       <c r="V23" s="17"/>
-      <c r="W23" s="17"/>
-      <c r="X23" s="18"/>
-    </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="W23" s="18"/>
+    </row>
+    <row r="24" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A24" s="15"/>
       <c r="B24" s="16"/>
       <c r="C24" s="17"/>
@@ -2290,14 +2251,13 @@
       <c r="P24" s="17"/>
       <c r="Q24" s="17"/>
       <c r="R24" s="17"/>
-      <c r="S24" s="17"/>
-      <c r="T24" s="18"/>
-      <c r="U24" s="16"/>
+      <c r="S24" s="18"/>
+      <c r="T24" s="16"/>
+      <c r="U24" s="17"/>
       <c r="V24" s="17"/>
-      <c r="W24" s="17"/>
-      <c r="X24" s="18"/>
-    </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="W24" s="18"/>
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A25" s="15"/>
       <c r="B25" s="16"/>
       <c r="C25" s="17"/>
@@ -2316,14 +2276,13 @@
       <c r="P25" s="17"/>
       <c r="Q25" s="17"/>
       <c r="R25" s="17"/>
-      <c r="S25" s="17"/>
-      <c r="T25" s="18"/>
-      <c r="U25" s="16"/>
+      <c r="S25" s="18"/>
+      <c r="T25" s="16"/>
+      <c r="U25" s="17"/>
       <c r="V25" s="17"/>
-      <c r="W25" s="17"/>
-      <c r="X25" s="18"/>
-    </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="W25" s="18"/>
+    </row>
+    <row r="26" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A26" s="15"/>
       <c r="B26" s="16"/>
       <c r="C26" s="17"/>
@@ -2342,14 +2301,13 @@
       <c r="P26" s="17"/>
       <c r="Q26" s="17"/>
       <c r="R26" s="17"/>
-      <c r="S26" s="17"/>
-      <c r="T26" s="18"/>
-      <c r="U26" s="16"/>
+      <c r="S26" s="18"/>
+      <c r="T26" s="16"/>
+      <c r="U26" s="17"/>
       <c r="V26" s="17"/>
-      <c r="W26" s="17"/>
-      <c r="X26" s="18"/>
-    </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="W26" s="18"/>
+    </row>
+    <row r="27" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A27" s="15"/>
       <c r="B27" s="16"/>
       <c r="C27" s="17"/>
@@ -2368,14 +2326,13 @@
       <c r="P27" s="17"/>
       <c r="Q27" s="17"/>
       <c r="R27" s="17"/>
-      <c r="S27" s="17"/>
-      <c r="T27" s="18"/>
-      <c r="U27" s="16"/>
+      <c r="S27" s="18"/>
+      <c r="T27" s="16"/>
+      <c r="U27" s="17"/>
       <c r="V27" s="17"/>
-      <c r="W27" s="17"/>
-      <c r="X27" s="18"/>
-    </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="W27" s="18"/>
+    </row>
+    <row r="28" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A28" s="15"/>
       <c r="B28" s="16"/>
       <c r="C28" s="17"/>
@@ -2394,14 +2351,13 @@
       <c r="P28" s="17"/>
       <c r="Q28" s="17"/>
       <c r="R28" s="17"/>
-      <c r="S28" s="17"/>
-      <c r="T28" s="18"/>
-      <c r="U28" s="16"/>
+      <c r="S28" s="18"/>
+      <c r="T28" s="16"/>
+      <c r="U28" s="17"/>
       <c r="V28" s="17"/>
-      <c r="W28" s="17"/>
-      <c r="X28" s="18"/>
-    </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="W28" s="18"/>
+    </row>
+    <row r="29" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A29" s="15"/>
       <c r="B29" s="16"/>
       <c r="C29" s="17"/>
@@ -2420,14 +2376,13 @@
       <c r="P29" s="17"/>
       <c r="Q29" s="17"/>
       <c r="R29" s="17"/>
-      <c r="S29" s="17"/>
-      <c r="T29" s="18"/>
-      <c r="U29" s="16"/>
+      <c r="S29" s="18"/>
+      <c r="T29" s="16"/>
+      <c r="U29" s="17"/>
       <c r="V29" s="17"/>
-      <c r="W29" s="17"/>
-      <c r="X29" s="18"/>
-    </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="W29" s="18"/>
+    </row>
+    <row r="30" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A30" s="15"/>
       <c r="B30" s="16"/>
       <c r="C30" s="17"/>
@@ -2446,14 +2401,13 @@
       <c r="P30" s="17"/>
       <c r="Q30" s="17"/>
       <c r="R30" s="17"/>
-      <c r="S30" s="17"/>
-      <c r="T30" s="18"/>
-      <c r="U30" s="16"/>
+      <c r="S30" s="18"/>
+      <c r="T30" s="16"/>
+      <c r="U30" s="17"/>
       <c r="V30" s="17"/>
-      <c r="W30" s="17"/>
-      <c r="X30" s="18"/>
-    </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="W30" s="18"/>
+    </row>
+    <row r="31" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A31" s="15"/>
       <c r="B31" s="16"/>
       <c r="C31" s="17"/>
@@ -2472,14 +2426,13 @@
       <c r="P31" s="17"/>
       <c r="Q31" s="17"/>
       <c r="R31" s="17"/>
-      <c r="S31" s="17"/>
-      <c r="T31" s="18"/>
-      <c r="U31" s="16"/>
+      <c r="S31" s="18"/>
+      <c r="T31" s="16"/>
+      <c r="U31" s="17"/>
       <c r="V31" s="17"/>
-      <c r="W31" s="17"/>
-      <c r="X31" s="18"/>
-    </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="W31" s="18"/>
+    </row>
+    <row r="32" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A32" s="15"/>
       <c r="B32" s="16"/>
       <c r="C32" s="17"/>
@@ -2498,14 +2451,13 @@
       <c r="P32" s="17"/>
       <c r="Q32" s="17"/>
       <c r="R32" s="17"/>
-      <c r="S32" s="17"/>
-      <c r="T32" s="18"/>
-      <c r="U32" s="16"/>
+      <c r="S32" s="18"/>
+      <c r="T32" s="16"/>
+      <c r="U32" s="17"/>
       <c r="V32" s="17"/>
-      <c r="W32" s="17"/>
-      <c r="X32" s="18"/>
-    </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="W32" s="18"/>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A33" s="15"/>
       <c r="B33" s="16"/>
       <c r="C33" s="17"/>
@@ -2524,14 +2476,13 @@
       <c r="P33" s="17"/>
       <c r="Q33" s="17"/>
       <c r="R33" s="17"/>
-      <c r="S33" s="17"/>
-      <c r="T33" s="18"/>
-      <c r="U33" s="16"/>
+      <c r="S33" s="18"/>
+      <c r="T33" s="16"/>
+      <c r="U33" s="17"/>
       <c r="V33" s="17"/>
-      <c r="W33" s="17"/>
-      <c r="X33" s="18"/>
-    </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="W33" s="18"/>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A34" s="15"/>
       <c r="B34" s="16"/>
       <c r="C34" s="17"/>
@@ -2550,14 +2501,13 @@
       <c r="P34" s="17"/>
       <c r="Q34" s="17"/>
       <c r="R34" s="17"/>
-      <c r="S34" s="17"/>
-      <c r="T34" s="18"/>
-      <c r="U34" s="16"/>
+      <c r="S34" s="18"/>
+      <c r="T34" s="16"/>
+      <c r="U34" s="17"/>
       <c r="V34" s="17"/>
-      <c r="W34" s="17"/>
-      <c r="X34" s="18"/>
-    </row>
-    <row r="35" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="W34" s="18"/>
+    </row>
+    <row r="35" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A35" s="15"/>
       <c r="B35" s="16"/>
       <c r="C35" s="17"/>
@@ -2576,14 +2526,13 @@
       <c r="P35" s="17"/>
       <c r="Q35" s="17"/>
       <c r="R35" s="17"/>
-      <c r="S35" s="17"/>
-      <c r="T35" s="18"/>
-      <c r="U35" s="16"/>
+      <c r="S35" s="18"/>
+      <c r="T35" s="16"/>
+      <c r="U35" s="17"/>
       <c r="V35" s="17"/>
-      <c r="W35" s="17"/>
-      <c r="X35" s="18"/>
-    </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="W35" s="18"/>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A36" s="15"/>
       <c r="B36" s="16"/>
       <c r="C36" s="17"/>
@@ -2602,14 +2551,13 @@
       <c r="P36" s="17"/>
       <c r="Q36" s="17"/>
       <c r="R36" s="17"/>
-      <c r="S36" s="17"/>
-      <c r="T36" s="18"/>
-      <c r="U36" s="16"/>
+      <c r="S36" s="18"/>
+      <c r="T36" s="16"/>
+      <c r="U36" s="17"/>
       <c r="V36" s="17"/>
-      <c r="W36" s="17"/>
-      <c r="X36" s="18"/>
-    </row>
-    <row r="37" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="W36" s="18"/>
+    </row>
+    <row r="37" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A37" s="15"/>
       <c r="B37" s="16"/>
       <c r="C37" s="17"/>
@@ -2628,14 +2576,13 @@
       <c r="P37" s="17"/>
       <c r="Q37" s="17"/>
       <c r="R37" s="17"/>
-      <c r="S37" s="17"/>
-      <c r="T37" s="18"/>
-      <c r="U37" s="16"/>
+      <c r="S37" s="18"/>
+      <c r="T37" s="16"/>
+      <c r="U37" s="17"/>
       <c r="V37" s="17"/>
-      <c r="W37" s="17"/>
-      <c r="X37" s="18"/>
-    </row>
-    <row r="38" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="W37" s="18"/>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A38" s="15"/>
       <c r="B38" s="16"/>
       <c r="C38" s="17"/>
@@ -2654,14 +2601,13 @@
       <c r="P38" s="17"/>
       <c r="Q38" s="17"/>
       <c r="R38" s="17"/>
-      <c r="S38" s="17"/>
-      <c r="T38" s="18"/>
-      <c r="U38" s="16"/>
+      <c r="S38" s="18"/>
+      <c r="T38" s="16"/>
+      <c r="U38" s="17"/>
       <c r="V38" s="17"/>
-      <c r="W38" s="17"/>
-      <c r="X38" s="18"/>
-    </row>
-    <row r="39" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="W38" s="18"/>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A39" s="15"/>
       <c r="B39" s="16"/>
       <c r="C39" s="17"/>
@@ -2680,14 +2626,13 @@
       <c r="P39" s="17"/>
       <c r="Q39" s="17"/>
       <c r="R39" s="17"/>
-      <c r="S39" s="17"/>
-      <c r="T39" s="18"/>
-      <c r="U39" s="16"/>
+      <c r="S39" s="18"/>
+      <c r="T39" s="16"/>
+      <c r="U39" s="17"/>
       <c r="V39" s="17"/>
-      <c r="W39" s="17"/>
-      <c r="X39" s="18"/>
-    </row>
-    <row r="40" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="W39" s="18"/>
+    </row>
+    <row r="40" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A40" s="15"/>
       <c r="B40" s="16"/>
       <c r="C40" s="17"/>
@@ -2706,14 +2651,13 @@
       <c r="P40" s="17"/>
       <c r="Q40" s="17"/>
       <c r="R40" s="17"/>
-      <c r="S40" s="17"/>
-      <c r="T40" s="18"/>
-      <c r="U40" s="16"/>
+      <c r="S40" s="18"/>
+      <c r="T40" s="16"/>
+      <c r="U40" s="17"/>
       <c r="V40" s="17"/>
-      <c r="W40" s="17"/>
-      <c r="X40" s="18"/>
-    </row>
-    <row r="41" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="W40" s="18"/>
+    </row>
+    <row r="41" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A41" s="15"/>
       <c r="B41" s="16"/>
       <c r="C41" s="17"/>
@@ -2732,14 +2676,13 @@
       <c r="P41" s="17"/>
       <c r="Q41" s="17"/>
       <c r="R41" s="17"/>
-      <c r="S41" s="17"/>
-      <c r="T41" s="18"/>
-      <c r="U41" s="16"/>
+      <c r="S41" s="18"/>
+      <c r="T41" s="16"/>
+      <c r="U41" s="17"/>
       <c r="V41" s="17"/>
-      <c r="W41" s="17"/>
-      <c r="X41" s="18"/>
-    </row>
-    <row r="42" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="W41" s="18"/>
+    </row>
+    <row r="42" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A42" s="15"/>
       <c r="B42" s="16"/>
       <c r="C42" s="17"/>
@@ -2758,14 +2701,13 @@
       <c r="P42" s="17"/>
       <c r="Q42" s="17"/>
       <c r="R42" s="17"/>
-      <c r="S42" s="17"/>
-      <c r="T42" s="18"/>
-      <c r="U42" s="16"/>
+      <c r="S42" s="18"/>
+      <c r="T42" s="16"/>
+      <c r="U42" s="17"/>
       <c r="V42" s="17"/>
-      <c r="W42" s="17"/>
-      <c r="X42" s="18"/>
-    </row>
-    <row r="43" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="W42" s="18"/>
+    </row>
+    <row r="43" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A43" s="15"/>
       <c r="B43" s="16"/>
       <c r="C43" s="17"/>
@@ -2784,14 +2726,13 @@
       <c r="P43" s="17"/>
       <c r="Q43" s="17"/>
       <c r="R43" s="17"/>
-      <c r="S43" s="17"/>
-      <c r="T43" s="18"/>
-      <c r="U43" s="16"/>
+      <c r="S43" s="18"/>
+      <c r="T43" s="16"/>
+      <c r="U43" s="17"/>
       <c r="V43" s="17"/>
-      <c r="W43" s="17"/>
-      <c r="X43" s="18"/>
-    </row>
-    <row r="44" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="W43" s="18"/>
+    </row>
+    <row r="44" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A44" s="15"/>
       <c r="B44" s="16"/>
       <c r="C44" s="17"/>
@@ -2810,14 +2751,13 @@
       <c r="P44" s="17"/>
       <c r="Q44" s="17"/>
       <c r="R44" s="17"/>
-      <c r="S44" s="17"/>
-      <c r="T44" s="18"/>
-      <c r="U44" s="16"/>
+      <c r="S44" s="18"/>
+      <c r="T44" s="16"/>
+      <c r="U44" s="17"/>
       <c r="V44" s="17"/>
-      <c r="W44" s="17"/>
-      <c r="X44" s="18"/>
-    </row>
-    <row r="45" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="W44" s="18"/>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A45" s="15"/>
       <c r="B45" s="16"/>
       <c r="C45" s="17"/>
@@ -2836,14 +2776,13 @@
       <c r="P45" s="17"/>
       <c r="Q45" s="17"/>
       <c r="R45" s="17"/>
-      <c r="S45" s="17"/>
-      <c r="T45" s="18"/>
-      <c r="U45" s="16"/>
+      <c r="S45" s="18"/>
+      <c r="T45" s="16"/>
+      <c r="U45" s="17"/>
       <c r="V45" s="17"/>
-      <c r="W45" s="17"/>
-      <c r="X45" s="18"/>
-    </row>
-    <row r="46" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="W45" s="18"/>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A46" s="15"/>
       <c r="B46" s="16"/>
       <c r="C46" s="17"/>
@@ -2862,14 +2801,13 @@
       <c r="P46" s="17"/>
       <c r="Q46" s="17"/>
       <c r="R46" s="17"/>
-      <c r="S46" s="17"/>
-      <c r="T46" s="18"/>
-      <c r="U46" s="16"/>
+      <c r="S46" s="18"/>
+      <c r="T46" s="16"/>
+      <c r="U46" s="17"/>
       <c r="V46" s="17"/>
-      <c r="W46" s="17"/>
-      <c r="X46" s="18"/>
-    </row>
-    <row r="47" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="W46" s="18"/>
+    </row>
+    <row r="47" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A47" s="15"/>
       <c r="B47" s="16"/>
       <c r="C47" s="17"/>
@@ -2888,14 +2826,13 @@
       <c r="P47" s="17"/>
       <c r="Q47" s="17"/>
       <c r="R47" s="17"/>
-      <c r="S47" s="17"/>
-      <c r="T47" s="18"/>
-      <c r="U47" s="16"/>
+      <c r="S47" s="18"/>
+      <c r="T47" s="16"/>
+      <c r="U47" s="17"/>
       <c r="V47" s="17"/>
-      <c r="W47" s="17"/>
-      <c r="X47" s="18"/>
-    </row>
-    <row r="48" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="W47" s="18"/>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A48" s="15"/>
       <c r="B48" s="16"/>
       <c r="C48" s="17"/>
@@ -2914,14 +2851,13 @@
       <c r="P48" s="17"/>
       <c r="Q48" s="17"/>
       <c r="R48" s="17"/>
-      <c r="S48" s="17"/>
-      <c r="T48" s="18"/>
-      <c r="U48" s="16"/>
+      <c r="S48" s="18"/>
+      <c r="T48" s="16"/>
+      <c r="U48" s="17"/>
       <c r="V48" s="17"/>
-      <c r="W48" s="17"/>
-      <c r="X48" s="18"/>
-    </row>
-    <row r="49" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="W48" s="18"/>
+    </row>
+    <row r="49" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A49" s="15"/>
       <c r="B49" s="16"/>
       <c r="C49" s="17"/>
@@ -2940,14 +2876,13 @@
       <c r="P49" s="17"/>
       <c r="Q49" s="17"/>
       <c r="R49" s="17"/>
-      <c r="S49" s="17"/>
-      <c r="T49" s="18"/>
-      <c r="U49" s="16"/>
+      <c r="S49" s="18"/>
+      <c r="T49" s="16"/>
+      <c r="U49" s="17"/>
       <c r="V49" s="17"/>
-      <c r="W49" s="17"/>
-      <c r="X49" s="18"/>
-    </row>
-    <row r="50" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="W49" s="18"/>
+    </row>
+    <row r="50" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A50" s="15"/>
       <c r="B50" s="16"/>
       <c r="C50" s="17"/>
@@ -2966,14 +2901,13 @@
       <c r="P50" s="17"/>
       <c r="Q50" s="17"/>
       <c r="R50" s="17"/>
-      <c r="S50" s="17"/>
-      <c r="T50" s="18"/>
-      <c r="U50" s="16"/>
+      <c r="S50" s="18"/>
+      <c r="T50" s="16"/>
+      <c r="U50" s="17"/>
       <c r="V50" s="17"/>
-      <c r="W50" s="17"/>
-      <c r="X50" s="18"/>
-    </row>
-    <row r="51" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="W50" s="18"/>
+    </row>
+    <row r="51" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A51" s="15"/>
       <c r="B51" s="16"/>
       <c r="C51" s="17"/>
@@ -2992,14 +2926,13 @@
       <c r="P51" s="17"/>
       <c r="Q51" s="17"/>
       <c r="R51" s="17"/>
-      <c r="S51" s="17"/>
-      <c r="T51" s="18"/>
-      <c r="U51" s="16"/>
+      <c r="S51" s="18"/>
+      <c r="T51" s="16"/>
+      <c r="U51" s="17"/>
       <c r="V51" s="17"/>
-      <c r="W51" s="17"/>
-      <c r="X51" s="18"/>
-    </row>
-    <row r="52" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="W51" s="18"/>
+    </row>
+    <row r="52" spans="1:23" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A52" s="23"/>
       <c r="B52" s="24"/>
       <c r="C52" s="25"/>
@@ -3018,20 +2951,19 @@
       <c r="P52" s="25"/>
       <c r="Q52" s="25"/>
       <c r="R52" s="25"/>
-      <c r="S52" s="25"/>
-      <c r="T52" s="26"/>
-      <c r="U52" s="24"/>
+      <c r="S52" s="26"/>
+      <c r="T52" s="24"/>
+      <c r="U52" s="25"/>
       <c r="V52" s="25"/>
-      <c r="W52" s="25"/>
-      <c r="X52" s="26"/>
+      <c r="W52" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="F1:L1"/>
-    <mergeCell ref="M1:T1"/>
-    <mergeCell ref="U1:X1"/>
+    <mergeCell ref="M1:S1"/>
+    <mergeCell ref="T1:W1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
